--- a/SGC-CKN/Excel/4541a8b0-ca78-4d25-84c5-9c38de60f807_Lô_CT-02_P_1_-_25_D800_23-03-2026.xlsx
+++ b/SGC-CKN/Excel/4541a8b0-ca78-4d25-84c5-9c38de60f807_Lô_CT-02_P_1_-_25_D800_23-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P.1 - 25</t>
+    <t>P7-25</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -239,7 +239,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -322,12 +322,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -338,7 +332,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,11 +412,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -518,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -628,16 +617,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1223,19 +1209,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="H11" s="5">
         <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>6.01</v>
+        <v>6.5</v>
       </c>
       <c r="J11" s="8">
-        <v>12.02</v>
+        <v>13</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1258,7 +1244,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="G12" s="9">
         <v>-8.5</v>
@@ -1267,10 +1253,10 @@
         <v>0.25</v>
       </c>
       <c r="I12" s="9">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J12" s="8">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1331,16 +1317,16 @@
         <v>-16.2</v>
       </c>
       <c r="G14" s="16">
-        <v>-20.8</v>
+        <v>-20.05</v>
       </c>
       <c r="H14" s="16">
         <v>1.5</v>
       </c>
       <c r="I14" s="16">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="J14" s="15">
-        <v>3.07</v>
+        <v>2.57</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1363,7 +1349,7 @@
         <v>42</v>
       </c>
       <c r="F15" s="19">
-        <v>-20.8</v>
+        <v>-20.05</v>
       </c>
       <c r="G15" s="19">
         <v>-24.5</v>
@@ -1372,10 +1358,10 @@
         <v>0.5</v>
       </c>
       <c r="I15" s="19">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="J15" s="8">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1506,16 +1492,16 @@
         <v>-40</v>
       </c>
       <c r="G19" s="31">
-        <v>-44.5</v>
+        <v>-44.3</v>
       </c>
       <c r="H19" s="31">
         <v>0.5</v>
       </c>
       <c r="I19" s="31">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J19" s="8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1538,7 +1524,7 @@
         <v>58</v>
       </c>
       <c r="F20" s="34">
-        <v>-44.5</v>
+        <v>-44.3</v>
       </c>
       <c r="G20" s="34">
         <v>-44.9</v>
@@ -1547,29 +1533,29 @@
         <v>0.42</v>
       </c>
       <c r="I20" s="34">
-        <v>0.4</v>
-      </c>
-      <c r="J20" s="37">
-        <v>0.96</v>
+        <v>0.6</v>
+      </c>
+      <c r="J20" s="15">
+        <v>1.44</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1705,19 +1691,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="G2" s="5">
         <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>6.01</v>
+        <v>6.5</v>
       </c>
       <c r="I2" s="8">
-        <v>12.02</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1734,7 +1720,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="F3" s="9">
         <v>-8.5</v>
@@ -1743,10 +1729,10 @@
         <v>0.25</v>
       </c>
       <c r="H3" s="9">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I3" s="8">
-        <v>6.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1795,16 +1781,16 @@
         <v>-16.2</v>
       </c>
       <c r="F5" s="16">
-        <v>-20.8</v>
+        <v>-20.05</v>
       </c>
       <c r="G5" s="16">
         <v>1.5</v>
       </c>
       <c r="H5" s="16">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="I5" s="15">
-        <v>3.07</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1821,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-20.8</v>
+        <v>-20.05</v>
       </c>
       <c r="F6" s="19">
         <v>-24.5</v>
@@ -1830,10 +1816,10 @@
         <v>0.5</v>
       </c>
       <c r="H6" s="19">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="I6" s="8">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1940,16 +1926,16 @@
         <v>-40</v>
       </c>
       <c r="F10" s="31">
-        <v>-44.5</v>
+        <v>-44.3</v>
       </c>
       <c r="G10" s="31">
         <v>0.5</v>
       </c>
       <c r="H10" s="31">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I10" s="8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1966,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-44.5</v>
+        <v>-44.3</v>
       </c>
       <c r="F11" s="34">
         <v>-44.9</v>
@@ -1975,39 +1961,39 @@
         <v>0.42</v>
       </c>
       <c r="H11" s="34">
-        <v>0.4</v>
-      </c>
-      <c r="I11" s="37">
-        <v>0.96</v>
+        <v>0.6</v>
+      </c>
+      <c r="I11" s="15">
+        <v>1.44</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
-        <v>-0.79</v>
-      </c>
-      <c r="F12" s="40">
+      <c r="E12" s="39">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39">
         <v>-44.9</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="39">
         <v>7.42</v>
       </c>
-      <c r="H12" s="40">
-        <v>44.11</v>
-      </c>
-      <c r="I12" s="40">
-        <v>5.95</v>
+      <c r="H12" s="39">
+        <v>44.9</v>
+      </c>
+      <c r="I12" s="39">
+        <v>6.05</v>
       </c>
     </row>
   </sheetData>
